--- a/plantillas/plantilla_cartera.xlsx
+++ b/plantillas/plantilla_cartera.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cartera" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Control" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +40,11 @@
     <font>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +66,11 @@
         <fgColor rgb="00FFF3C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -75,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +96,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -538,6 +550,13 @@
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Sirve con cualquier programa contable: exporte la cartera a Excel y copie los valores en estas columnas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hoja Control (celdas amarillas): la llena la contadora con los totales del informe contable. La usa el programa del PC de la administración; en el panel, los totales se escriben a mano.</t>
         </is>
       </c>
     </row>
@@ -2058,4 +2077,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>dato</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>qué es</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_informe</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Total de la cartera según el informe contable (en pesos, sin decimales)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Si el total del archivo no es igual a este valor, no se publica nada.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>